--- a/artfynd/A 34855-2022 artfynd.xlsx
+++ b/artfynd/A 34855-2022 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136687168</v>
       </c>
       <c r="B3" t="n">
-        <v>61562</v>
+        <v>61564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
